--- a/Solver.xlsx
+++ b/Solver.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCDB13C0-1433-42C8-B8BB-C86116E7CFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63C3905-4795-44DE-87E6-E202F84413F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{02A40CC1-0F81-4A59-A5C9-979AEF35C4D8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{02A40CC1-0F81-4A59-A5C9-979AEF35C4D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic Solver" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Min Solver" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'Basic Solver'!$B$2:$B$5</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -63,12 +64,13 @@
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Basic Solver'!$D$6</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -120,10 +122,10 @@
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">2000</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
@@ -149,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>Particulars</t>
   </si>
@@ -251,6 +253,114 @@
   </si>
   <si>
     <t>Total Cost of Shipping</t>
+  </si>
+  <si>
+    <t>go to file</t>
+  </si>
+  <si>
+    <t>click options</t>
+  </si>
+  <si>
+    <t>then click add-is</t>
+  </si>
+  <si>
+    <t>then click  manage, there select Excel Add-ins</t>
+  </si>
+  <si>
+    <t>click ok</t>
+  </si>
+  <si>
+    <t>select the solver Add-in</t>
+  </si>
+  <si>
+    <t>now it is visible in data tab</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>How to add solver in Data tab ?</t>
+  </si>
+  <si>
+    <t>click solver</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">then set the objective cell </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i.e., here grand total cell d6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">select to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>value of</t>
+    </r>
+  </si>
+  <si>
+    <t>then select the changing varaiable</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">select the solving method to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> GRG Nonliner</t>
+    </r>
+  </si>
+  <si>
+    <t>then click solve</t>
+  </si>
+  <si>
+    <t>here the value will solve, but it will be in float value.</t>
+  </si>
+  <si>
+    <t>to change it into integer.</t>
+  </si>
+  <si>
+    <t>after this</t>
+  </si>
+  <si>
+    <t>click add on the constraints</t>
+  </si>
+  <si>
+    <t>there select the cell reference</t>
+  </si>
+  <si>
+    <t>then click add</t>
+  </si>
+  <si>
+    <t>then ok</t>
+  </si>
+  <si>
+    <t>it will change to integer.</t>
   </si>
 </sst>
 </file>
@@ -712,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031F83FC-4A7A-47CB-A649-2EE8D76905B2}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
@@ -721,7 +831,7 @@
     <col min="4" max="4" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -735,22 +845,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>850</v>
       </c>
       <c r="D2">
         <f>B2*C2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -764,52 +874,147 @@
         <f t="shared" ref="D3:D5" si="0">B3*C3</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>200</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>475</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>950</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <f>SUM(D2:D5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+        <v>2000</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="I8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9">
         <v>2000</v>
+      </c>
+      <c r="N9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="I11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Solver.xlsx
+++ b/Solver.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63C3905-4795-44DE-87E6-E202F84413F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7830D595-35B4-4035-9EEE-325F7F4DB7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{02A40CC1-0F81-4A59-A5C9-979AEF35C4D8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{02A40CC1-0F81-4A59-A5C9-979AEF35C4D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic Solver" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Basic Solver'!$B$2:$B$5</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">'Max Solver'!$B$2:$B$4</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -38,12 +39,13 @@
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'Max Solver'!$B$2</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Min Solver'!$B$4:$E$4</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Basic Solver'!$B$2:$B$5</definedName>
-    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'Max Solver'!$B$3</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'Max Solver'!$B$2:$B$4</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">'Min Solver'!$B$4:$E$6</definedName>
-    <definedName name="solver_lhs3" localSheetId="1" hidden="1">'Max Solver'!$B$4</definedName>
+    <definedName name="solver_lhs3" localSheetId="1" hidden="1">'Max Solver'!$B$3</definedName>
     <definedName name="solver_lhs3" localSheetId="2" hidden="1">'Min Solver'!$B$4:$E$6</definedName>
-    <definedName name="solver_lhs4" localSheetId="1" hidden="1">'Max Solver'!$B$5</definedName>
+    <definedName name="solver_lhs4" localSheetId="1" hidden="1">'Max Solver'!$B$4</definedName>
     <definedName name="solver_lhs4" localSheetId="2" hidden="1">'Min Solver'!$B$5:$E$5</definedName>
+    <definedName name="solver_lhs5" localSheetId="1" hidden="1">'Max Solver'!$B$5</definedName>
     <definedName name="solver_lhs5" localSheetId="2" hidden="1">'Min Solver'!$B$6:$E$6</definedName>
     <definedName name="solver_lhs6" localSheetId="2" hidden="1">'Min Solver'!$B$7:$E$7</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
@@ -65,12 +67,13 @@
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">5</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Basic Solver'!$D$6</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">'Max Solver'!$D$5</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -81,24 +84,26 @@
     <definedName name="solver_rel1" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="1" hidden="1">4</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">4</definedName>
     <definedName name="solver_rel3" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="2" hidden="1">3</definedName>
-    <definedName name="solver_rel4" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_rel4" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rel5" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel6" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">"integer"</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">92</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">20</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">"integer"</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">"integer"</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">50</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">20</definedName>
     <definedName name="solver_rhs3" localSheetId="2" hidden="1">20</definedName>
-    <definedName name="solver_rhs4" localSheetId="1" hidden="1">350</definedName>
+    <definedName name="solver_rhs4" localSheetId="1" hidden="1">50</definedName>
     <definedName name="solver_rhs4" localSheetId="2" hidden="1">45</definedName>
+    <definedName name="solver_rhs5" localSheetId="1" hidden="1">350</definedName>
     <definedName name="solver_rhs5" localSheetId="2" hidden="1">55</definedName>
     <definedName name="solver_rhs6" localSheetId="2" hidden="1">'Min Solver'!$B$8:$E$8</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
@@ -151,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t>Particulars</t>
   </si>
@@ -1050,10 +1055,14 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>10</v>
+      </c>
+      <c r="D2">
+        <f>B2*C2</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1061,10 +1070,14 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>16</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D4" si="0">B3*C3</f>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -1072,15 +1085,30 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="C4">
         <v>33</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>7590</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>350</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5">
+        <f>SUM(D2:D4)</f>
+        <v>8910</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
